--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.30088359901244</v>
+        <v>5.248893584839522</v>
       </c>
       <c r="D2" t="n">
-        <v>24.06389568586276</v>
+        <v>3.910383048952699</v>
       </c>
       <c r="E2" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F2" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.37870945219902</v>
+        <v>5.09904028598234</v>
       </c>
       <c r="D3" t="n">
-        <v>31.01752434061898</v>
+        <v>5.040347705350584</v>
       </c>
       <c r="E3" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F3" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.63791666848225</v>
+        <v>4.653661458628365</v>
       </c>
       <c r="D4" t="n">
-        <v>28.87145371341784</v>
+        <v>4.6916112284304</v>
       </c>
       <c r="E4" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F4" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.45007845828165</v>
+        <v>5.598137749470768</v>
       </c>
       <c r="D5" t="n">
-        <v>26.35743717795221</v>
+        <v>4.283083541417235</v>
       </c>
       <c r="E5" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F5" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.90431805090513</v>
+        <v>5.509451683272083</v>
       </c>
       <c r="D6" t="n">
-        <v>31.30341090706445</v>
+        <v>5.086804272397973</v>
       </c>
       <c r="E6" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F6" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.90870104199842</v>
+        <v>6.972663919324743</v>
       </c>
       <c r="D7" t="n">
-        <v>42.43295603481445</v>
+        <v>6.895355355657347</v>
       </c>
       <c r="E7" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F7" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.41466094233228</v>
+        <v>6.242382403128995</v>
       </c>
       <c r="D8" t="n">
-        <v>27.67384413723379</v>
+        <v>4.496999672300491</v>
       </c>
       <c r="E8" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F8" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.1125697513158</v>
+        <v>7.493292584588817</v>
       </c>
       <c r="D9" t="n">
-        <v>32.85663771561705</v>
+        <v>5.339203628787771</v>
       </c>
       <c r="E9" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F9" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.4258409230041</v>
+        <v>6.244199149988166</v>
       </c>
       <c r="D10" t="n">
-        <v>15.1539998402215</v>
+        <v>2.462524974035994</v>
       </c>
       <c r="E10" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F10" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.29640101788985</v>
+        <v>3.460665165407101</v>
       </c>
       <c r="D11" t="n">
-        <v>12.0415945787923</v>
+        <v>1.956759119053748</v>
       </c>
       <c r="E11" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F11" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.71191405615481</v>
+        <v>5.803186034125157</v>
       </c>
       <c r="D12" t="n">
-        <v>27.04163456597992</v>
+        <v>4.394265616971737</v>
       </c>
       <c r="E12" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F12" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.02889513331213</v>
+        <v>3.904695459163221</v>
       </c>
       <c r="D13" t="n">
-        <v>24.24257279893654</v>
+        <v>3.939418079827188</v>
       </c>
       <c r="E13" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F13" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>45.44710226649909</v>
+        <v>7.385154118306102</v>
       </c>
       <c r="D14" t="n">
-        <v>41.51002394082106</v>
+        <v>6.745378890383422</v>
       </c>
       <c r="E14" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F14" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>62.37305905839293</v>
+        <v>10.13562209698885</v>
       </c>
       <c r="D15" t="n">
-        <v>62.23636485311766</v>
+        <v>10.11340928863162</v>
       </c>
       <c r="E15" t="n">
-        <v>9.974422910448322</v>
+        <v>1.620843722947853</v>
       </c>
       <c r="F15" t="n">
-        <v>11.87382753406032</v>
+        <v>1.929496974284801</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
